--- a/order_forms/038_sports_club_refreshment_supply_order_form--order_forms.xlsx
+++ b/order_forms/038_sports_club_refreshment_supply_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'beverages'}</t>
+          <t>beverages</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Beverages'}</t>
+          <t>Beverages</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'member'}</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Member'}</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
